--- a/questions_answers_for_new_student.xlsx
+++ b/questions_answers_for_new_student.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5672F32-96E3-4F42-AB85-710B97F43569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$27</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>question</t>
   </si>
@@ -118,9 +132,6 @@
     <t>No, you have to complete the course in which you are being enrolled. After three months of your course completion you can get enrolled for another course.</t>
   </si>
   <si>
-    <t>Yes, Anudip is an inclusive organization. Please contact the Centre Faculty to enquire if there are relevant courses operational for PWD youths.</t>
-  </si>
-  <si>
     <t>All our learning content is available on Learning Management System</t>
   </si>
   <si>
@@ -176,13 +187,22 @@
   </si>
   <si>
     <t>If your concern is not listed please contact your faculty for any concern/support/guidance</t>
+  </si>
+  <si>
+    <t>Anudip Foundation offers a wide range of skill-development, digital literacy, and technology courses designed to enhance employability.
+AI Readiness, Workplace IT (WPI) for basic computer skills, MS Office proficiency, and Workplace Readiness training, specialized BFSI programs, Advanced Frontend Development with AI, Advanced Java Development with AI, Java Full Stack with Angular and AI, and Java &amp; Web Development Fundamentals with AI.
+Refer to the link for more details: Courses - Anudip</t>
+  </si>
+  <si>
+    <t>Yes, Anudip Foundation provides dedicated support for specially-abled individuals to ensure an inclusive learning environment.
+Through initiatives like our SAVE (Specially Abled Vocational Education) program, we offer:Assistive Technologies: Access to tools like screen readers (JAWS/NVDA), voice commands, adaptive keyboards, and specialized learning materials tailored to visually, hearing, or physically challenged students. Accessible Learning &amp; Infrastructure: Physical centers equipped with ramps and accessible facilities, as well as options for flexible, home-based online sessions.Personalized Mentorship: Tailored coaching, soft-skills training, and pace-adjusted learning tailored to your specific needs.Inclusive Career &amp; Remote Job Opportunities: Focused job-readiness training, mock interview preparation, and placement support targeting accessible and work-from-home roles with partner companies.Refer to the link for more details: https://aadi.org/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,10 +254,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -245,6 +268,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -291,7 +322,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -323,9 +354,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -357,6 +406,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -532,11 +599,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="16384" width="8.7265625" style="2"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -547,215 +617,216 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:3" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+    <row r="5" spans="1:3" ht="246.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
+    <row r="6" spans="1:3" ht="304.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+    <row r="7" spans="1:3" ht="304.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
+    <row r="8" spans="1:3" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="145" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" t="s">
+    <row r="10" spans="1:3" ht="362.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="11" spans="1:3" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="12" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
+    <row r="13" spans="1:3" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
+    <row r="14" spans="1:3" ht="203" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
+    <row r="15" spans="1:3" ht="362.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="16" spans="1:3" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="17" spans="1:2" ht="145" x14ac:dyDescent="0.35">
+      <c r="A17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="18" spans="1:2" ht="275.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
+    <row r="19" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="20" spans="1:2" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" t="s">
+    <row r="21" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="22" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="23" spans="1:2" ht="409.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
+    <row r="24" spans="1:2" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" t="s">
+    <row r="25" spans="1:2" ht="290" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="26" spans="1:2" ht="217.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" t="s">
+    <row r="27" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+      <c r="A27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:C27" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/questions_answers_for_new_student.xlsx
+++ b/questions_answers_for_new_student.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chataddb\stubot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5672F32-96E3-4F42-AB85-710B97F43569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F6C0BD0-17B3-4E8A-9E66-4A4DA1A98100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -189,13 +189,13 @@
     <t>If your concern is not listed please contact your faculty for any concern/support/guidance</t>
   </si>
   <si>
+    <t>Yes, Anudip Foundation provides dedicated support for specially-abled individuals to ensure an inclusive learning environment.
+Through initiatives like our SAVE (Specially Abled Vocational Education) program, we offer:Assistive Technologies: Access to tools like screen readers (JAWS/NVDA), voice commands, adaptive keyboards, and specialized learning materials tailored to visually, hearing, or physically challenged students. Accessible Learning &amp; Infrastructure: Physical centers equipped with ramps and accessible facilities, as well as options for flexible, home-based online sessions.Personalized Mentorship: Tailored coaching, soft-skills training, and pace-adjusted learning tailored to your specific needs.Inclusive Career &amp; Remote Job Opportunities: Focused job-readiness training, mock interview preparation, and placement support targeting accessible and work-from-home roles with partner companies.Refer to the link for more details: https://aadi.org/</t>
+  </si>
+  <si>
     <t>Anudip Foundation offers a wide range of skill-development, digital literacy, and technology courses designed to enhance employability.
 AI Readiness, Workplace IT (WPI) for basic computer skills, MS Office proficiency, and Workplace Readiness training, specialized BFSI programs, Advanced Frontend Development with AI, Advanced Java Development with AI, Java Full Stack with Angular and AI, and Java &amp; Web Development Fundamentals with AI.
-Refer to the link for more details: Courses - Anudip</t>
-  </si>
-  <si>
-    <t>Yes, Anudip Foundation provides dedicated support for specially-abled individuals to ensure an inclusive learning environment.
-Through initiatives like our SAVE (Specially Abled Vocational Education) program, we offer:Assistive Technologies: Access to tools like screen readers (JAWS/NVDA), voice commands, adaptive keyboards, and specialized learning materials tailored to visually, hearing, or physically challenged students. Accessible Learning &amp; Infrastructure: Physical centers equipped with ramps and accessible facilities, as well as options for flexible, home-based online sessions.Personalized Mentorship: Tailored coaching, soft-skills training, and pace-adjusted learning tailored to your specific needs.Inclusive Career &amp; Remote Job Opportunities: Focused job-readiness training, mock interview preparation, and placement support targeting accessible and work-from-home roles with partner companies.Refer to the link for more details: https://aadi.org/</t>
+Refer to the link for more details: https://learn.anudip.org/</t>
   </si>
 </sst>
 </file>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="409.5" x14ac:dyDescent="0.35">
@@ -670,7 +670,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="145" x14ac:dyDescent="0.35">
